--- a/data/Vectores_Enaproce_2026_220526.xlsx
+++ b/data/Vectores_Enaproce_2026_220526.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cristina.sanchez\Documents\VALIDADOR_VECTORES\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cristina.sanchez\Documents\VECTORES_ARCHIVOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DAFD51-5197-49D8-BE3C-E05BA098AFD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC366D95-5436-482F-9EC9-343509EE779E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6E733D8A-4C45-43D2-B2AD-7E346F50450A}"/>
   </bookViews>
@@ -76,13 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="107">
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>E_ENAPROCE_01H01</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="159">
   <si>
     <t>O</t>
   </si>
@@ -114,19 +108,10 @@
     <t>E_ENAPROCE_09O01</t>
   </si>
   <si>
-    <t>E_ENAPROCE_10H01</t>
-  </si>
-  <si>
     <t>E_ENAPROCE_11O01</t>
   </si>
   <si>
     <t>E_ENAPROCE_12I01</t>
-  </si>
-  <si>
-    <t>E_ENAPROCE_13H01</t>
-  </si>
-  <si>
-    <t>E_ENAPROCE_13H02</t>
   </si>
   <si>
     <t>E_ENAPROCE_14I01</t>
@@ -209,9 +194,6 @@
   <si>
     <t>FILTRO / PRECONDICIÓN
 ENAPROCE 2026</t>
-  </si>
-  <si>
-    <t>P1A_HIST&lt;&gt;NULL AND P1A_HIST&gt;0</t>
   </si>
   <si>
     <t>P2_9&gt;0</t>
@@ -237,17 +219,7 @@
     <t>P9_9=1</t>
   </si>
   <si>
-    <t>P10_HIST&lt;&gt;NULL AND
-P10_HIST&lt;&gt;2</t>
-  </si>
-  <si>
     <t>P11=9</t>
-  </si>
-  <si>
-    <t>P13_0_HIST&lt;&gt;NULL AND P13_0_HIST&gt;0</t>
-  </si>
-  <si>
-    <t>ESTRATO&lt;&gt;NULL AND ESTRATO&gt;0 AND P13_0CAL&lt;&gt;NULL AND P13_0CAL&gt;0</t>
   </si>
   <si>
     <t xml:space="preserve">P6_1=2
@@ -305,24 +277,12 @@
 ENAPROCE 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">
-P1A-P1A_HIST&lt;&gt;0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-P2_9X&lt;&gt;NULL</t>
-  </si>
-  <si>
     <t>P3_19X&lt;&gt;NULL</t>
   </si>
   <si>
     <t>P4_9X&lt;&gt;NULL</t>
   </si>
   <si>
-    <t xml:space="preserve">P5_9X&lt;&gt;NULL
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">P6_4_1=0 </t>
   </si>
   <si>
@@ -333,9 +293,6 @@
   </si>
   <si>
     <t>P9_9X&lt;&gt;NULL</t>
-  </si>
-  <si>
-    <t>P10&lt;&gt;P10_HIST</t>
   </si>
   <si>
     <t xml:space="preserve">P11_9X&lt;&gt;NULL
@@ -347,12 +304,6 @@
 </t>
   </si>
   <si>
-    <t>(((P13_0/P13_0_HIST)-1)*100)&lt;-N OR (((P13_0/P13_0_HIST)-1)*100)&gt;N</t>
-  </si>
-  <si>
-    <t>P13_0CAL &lt;&gt; ESTRATO</t>
-  </si>
-  <si>
     <t xml:space="preserve">P14_1B=0 </t>
   </si>
   <si>
@@ -368,15 +319,10 @@
     <t>P16_9X&lt;&gt;NULL</t>
   </si>
   <si>
+    <t>(((P17_1+P17_2)/P13_1_1)/12)&lt;1050 OR (((P17_1+P17_2)/P13_1_1)/12)&gt;60000</t>
+  </si>
+  <si>
     <t>(P17_1/P14_1A)&lt;=(P17_2/P14_2A)</t>
-  </si>
-  <si>
-    <t>P17_1=0
-P17_1&gt;0</t>
-  </si>
-  <si>
-    <t>P17_2=0
-P17_2&gt;0</t>
   </si>
   <si>
     <t xml:space="preserve">P18_9X&lt;&gt;NULL
@@ -389,42 +335,323 @@
     <t>P20_2&gt;=(P17_1+P17_2)</t>
   </si>
   <si>
-    <t xml:space="preserve">P20_2&gt;0 AND P20_2&lt;=10
+    <t>P14_1B=0</t>
+  </si>
+  <si>
+    <t>P14_2A=0</t>
+  </si>
+  <si>
+    <t>P14_2B=0</t>
+  </si>
+  <si>
+    <t>P20_3&gt;0 AND P20_3&lt;=10</t>
+  </si>
+  <si>
+    <t>P21_19X&lt;&gt;NULL</t>
+  </si>
+  <si>
+    <t>VARIABLES INVOLUCRADAS
+ENAPROCE 2026</t>
+  </si>
+  <si>
+    <t>P2_9
+P2_9X</t>
+  </si>
+  <si>
+    <t>P3_1
+P3_2
+P3_3
+P3_19X</t>
+  </si>
+  <si>
+    <t>P4
+P4_9X</t>
+  </si>
+  <si>
+    <t>P5
+P5_9X</t>
+  </si>
+  <si>
+    <t>P6_1
+P6_4_1</t>
+  </si>
+  <si>
+    <t>P6_1
+P6_4_2</t>
+  </si>
+  <si>
+    <t>P9_1</t>
+  </si>
+  <si>
+    <t>P9_9
+P9_9X</t>
+  </si>
+  <si>
+    <t>P11
+P11_9X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P12
 </t>
   </si>
   <si>
-    <t>P20_1_0A&gt;P13_0</t>
-  </si>
-  <si>
-    <t>P20_1_1A&gt;P14_1A</t>
-  </si>
-  <si>
-    <t>P20_1_2A&gt;P14_2A</t>
-  </si>
-  <si>
-    <t>P14_1B=0</t>
-  </si>
-  <si>
-    <t>P14_2A=0</t>
-  </si>
-  <si>
-    <t>P14_2B=0</t>
-  </si>
-  <si>
-    <t>P20_3&gt;0 AND P20_3&lt;=10</t>
-  </si>
-  <si>
-    <t>P21_19X&lt;&gt;NULL</t>
-  </si>
-  <si>
-    <t>(((P17_1+P17_2)/P13_1_1)/12 &lt; 1050 or ((P17_1+P17_2)/P13_1_1)/12 &gt; 60000)</t>
+    <t xml:space="preserve">P6_1
+P14_1B
+</t>
+  </si>
+  <si>
+    <t>P5
+P14_1A</t>
+  </si>
+  <si>
+    <t>P4
+P14_1A</t>
+  </si>
+  <si>
+    <t>P13_0
+P15_1</t>
+  </si>
+  <si>
+    <t>P16
+P16_9X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P13_1_1
+P17_1
+P17_2
+</t>
+  </si>
+  <si>
+    <t>P13_1_1
+P14_1A
+P14_2A
+P17_1
+P17_2</t>
+  </si>
+  <si>
+    <t>P14_1A
+P17_1</t>
+  </si>
+  <si>
+    <t>P14_2A
+P17_2</t>
+  </si>
+  <si>
+    <t>P18
+P18_9X</t>
+  </si>
+  <si>
+    <t>P13_1_1
+P18</t>
+  </si>
+  <si>
+    <t>P13_1_1
+P17_1
+P17_2
+P20_2</t>
+  </si>
+  <si>
+    <t>P19
+P20_2</t>
+  </si>
+  <si>
+    <t>P13_0
+P20_1_0A</t>
+  </si>
+  <si>
+    <t>P14_1A
+P20_1_1A</t>
+  </si>
+  <si>
+    <t>P14_2A
+P20_1_2A</t>
+  </si>
+  <si>
+    <t>P14_1B
+P20_1_1B</t>
+  </si>
+  <si>
+    <t>P14_2B
+P20_1_2B</t>
+  </si>
+  <si>
+    <t>P20_3</t>
+  </si>
+  <si>
+    <t>P21
+P21_19X</t>
+  </si>
+  <si>
+    <t>PROCEDIMIENTO
+ENAPROCE 2026</t>
+  </si>
+  <si>
+    <t>02O01_2 Revisa la descripción de la opción «Otra» de las fuentes que recibió capital cuando inició la empresa, con el fin de identificar si puede reclasificarse en alguno de los incisos anteriores. 
+Acepta justificación, «Sin posibilidad de ser reclasificado».</t>
+  </si>
+  <si>
+    <t>03O01_2 Revisa la descripción de «Otro» de los tres factores más importantes para determinar la ubicación actual de la empresa, con el fin de identificar si se puede reclasificar en los incisos anteriores.
+Acepta justificación, «Sin posibilidad de ser reclasificado».</t>
+  </si>
+  <si>
+    <t>04O01_2 Revisa la descripción de «Otro(a)» propietarios(as) o accionistas mayoritarios(as) de la empresa, con el fin de identificar si se puede reclasificar en los incisos anteriores. 
+Acepta justificación, «Sin posibilidad de ser reclasificado».</t>
+  </si>
+  <si>
+    <t>05O01_2 Revisa la descripción de «Otro(a)» quién o quiénes toman principalmente las decisiones de la empresa, con el fin de identificar si se puede reclasificar en los incisos anteriores.
+Acepta justificación, «Sin posibilidad de ser reclasificado».</t>
+  </si>
+  <si>
+    <t>06I01_2  Reconsulta con la persona informante si la persona que toma principalmente las decisiones de la empresa es hombre, ya que menciona que el porcentaje de propiedad de la empresa que está en manos de hombres es cero. De ser necesario, corrige las variables involucradas.
+Acepta justificación.</t>
+  </si>
+  <si>
+    <t>06I02_2  Reconsulta con la persona informante si la persona que toma principalmente las decisiones de la empresa es mujer, ya que menciona que el porcentaje de propiedad de la empresa que está en manos de mujeres es cero. De ser necesario, corrige las variables involucradas.
+Acepta justificación</t>
+  </si>
+  <si>
+    <t>09I01_2 Reconsulta con la persona informante el motivo por el cual la empresa no acepta efectivo como forma de pago por los productos (bienes o servicios) que ofrece.
+Acepta justificación.</t>
+  </si>
+  <si>
+    <t>09O01_2 Revisa la descripción de «Otro» medio de pago que acepta la empresa por los productos (bienes o servicios) que ofrece, con el fin de identificar si se puede reclasificar en los incisos anteriores.
+Acepta justificación, «Sin posibilidad de ser reclasificado».</t>
+  </si>
+  <si>
+    <t>11O01_2 Revisa la descripción de «Otro» principal motivo por el que la empresa no es proveedora del gobierno, con el fin de identificar si se puede reclasificar en los incisos anteriores.
+Acepta justificación, «Sin posibilidad de ser reclasificado».</t>
+  </si>
+  <si>
+    <t>12I01_2 Reconsulta con la persona informante el motivo por el cual la empresa reportó haber trabajado en promedio de 10 a 47 horas a la semana durante el año 2025.
+Acepta justificación.
+12I01_3 Reconsulta con la persona informante el motivo por el cual la empresa reportó trabajar en promedio menos de 10 horas a la semana durante el año 2025.
+Acepta justificación.</t>
+  </si>
+  <si>
+    <t>14I01_2 Reconsulta con la persona informante el motivo por el cual indica que la persona que toma principalmente las decisiones de la empresa es mujer, y el personal directivo y de supervisión que son mujeres es igual a cero.
+Acepta justificación.</t>
+  </si>
+  <si>
+    <t>14I02_2 Reconsulta con la persona informante el motivo por el cual se reportó que el gerente o director general es quien toma las decisiones de la empresa, y el personal directivo y de supervisión es igual a cero.
+Acepta justificación.</t>
+  </si>
+  <si>
+    <t>14I03_2 Reconsulta con la persona informante el motivo por el cual indicó que el principal propietario o accionista mayoritario de la empresa es la persona directora general o gerente, y no reportó personal directivo y de supervisión.</t>
+  </si>
+  <si>
+    <t>15I01_2 Reconsulta con la persona informante el motivo por el cual el porcentaje de personal por nivel de estudios (sin instrucción) es mayor al 10 % del total del personal durante el año 2025.
+Acepta justificación.</t>
+  </si>
+  <si>
+    <t>16O01_2 Revisa la descripción de «Otra» principal carencia del personal que contrata la empresa, con el fin de identificar si se puede reclasificar en los incisos anteriores.
+Acepta justificación, «Sin posibilidad de ser reclasificado».</t>
+  </si>
+  <si>
+    <t>17I01_2 Reconsulta con la persona informante la cantidad correcta de las remuneraciones anuales pagadas, así como el personal ocupado dependiente de la razón social durante el año 2025. Asimismo, verifica que las remuneraciones se encuentren expresadas en pesos, ya que los montos reportados podrían resultar muy bajos o muy altos para el año 2025, así como el número de meses laborados por la empresa en dicho año.
+Acepta justificación.</t>
+  </si>
+  <si>
+    <t>17I02_2 Reconsulta con la persona informante el motivo por el cual la remuneración promedio anual pagada al personal directivo y de supervisión es menor o igual que la remuneración promedio anual pagada al personal operativo y de apoyo en el año 2025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17I03_2 Reconsulta con la persona informante ambas variables, ya que reportó remuneraciones para el personal directivo y de supervisión y no registró personal ocupado en este tipo de función durante el año 2025.
+17I03_3 Reconsulta con la persona informante ambas variables, ya que reportó personal directivo y de supervisión y no registró el pago total de remuneraciones anuales a este personal durante el año 2025.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17I04_2 Reconsulta con la persona informante ambas variables, ya que reportó remuneraciones para el personal operativo y de apoyo y no registró personal ocupado en este tipo de función durante el año 2025.
+17I04_3 Reconsulta con la persona informante ambas variables, ya que reportó personal operativo y de apoyo y no registró el pago total de remuneraciones anuales a este personal durante el año 2025.  </t>
+  </si>
+  <si>
+    <t>18O01_2 Revisa la descripción de «Otra» frecuencia con la que se le pagó principalmente a la mayoría del personal que laboró en la empresa durante el año 2025, con el fin de identificar si se puede reclasificar en los incisos anteriores.
+Acepta justificación, «Sin posibilidad de ser reclasificado».</t>
+  </si>
+  <si>
+    <t>18I01_2 Reconsulta con la persona informante si la empresa cuenta con personal remunerado dependiente de la razón social, ya que en la frecuencia de pago al personal que laboró en la empresa indicó que no dispone de personal remunerado. De ser necesario, corrige las variables involucradas.</t>
+  </si>
+  <si>
+    <t>20I01_2 Reconsulta con la persona informante el motivo por el cual el gasto total realizado en capacitación es mayor o igual a las remuneraciones anuales pagadas por la empresa durante el año 2025.
+Acepta justificación.</t>
+  </si>
+  <si>
+    <t>20I02_2 Reconsulta con la persona informante el motivo por el cual, en el gasto total realizado en capacitación por la empresa durante el año 2025, se reportó un monto menor o igual a 10 pesos. 
+Deberás verificar que el resto de las variables monetarias se encuentren reportadas en pesos y no en miles de pesos. 
+Acepta justificación.</t>
+  </si>
+  <si>
+    <t>20I03_2 Reconsulta con la persona informante que ambas cantidades sean correctas, de ser así, solicita el motivo por el cual el número del personal total capacitado por la empresa es mayor al promedio total del personal ocupado dependiente y no dependiente de la razón social durante el año 2025. De ser necesario, corrige las variable involucradas.</t>
+  </si>
+  <si>
+    <t>20I04_2 Reconsulta con la persona informante que ambas cantidades sean correctas, de ser así, solicita el motivo por el cual el personal directivo y de supervisión capacitado es mayor que el personal ocupado dependiente y no dependiente de la razón social, correspondiente a la función de «Personal Directivo y de  Supervisión».
+De ser necesario, corrige las variables involucradas.</t>
+  </si>
+  <si>
+    <t>20I05_ 2 Reconsulta con la persona informante que ambas cantidades sean correctas, de ser así, solicita el motivo por el cual el personal operativo y de apoyo capacitado es mayor que el personal ocupado dependiente y no dependiente de la razón social, correspondiente a la función de «Personal Operativo y de Apoyo».
+De ser necesario, corrige las variables involucradas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20I06_2 Reconsulta con la persona informante ambas variables, ya que reportó personal capacitado en funciones directivas y de supervisión y no reporta personal ocupado, dependiente y no dependiente de la razón social, en dichas funciones durante el año 2025. Corrige las variables involucradas.
+</t>
+  </si>
+  <si>
+    <t>20I07_2 Reconsulta con la persona informante ambas variables, ya que reportó personal capacitado en funciones directivas y de supervisión que son mujeres y no reportó personal ocupado en funciones directivas y de supervisión, dependiente y no dependiente de la razón social, que son mujeres durante el año 2025. Corrige las variables involucradas.</t>
+  </si>
+  <si>
+    <t>20I08_2 Reconsulta con la persona informante ambas variables, ya que reportó personal capacitado en funciones operativas y de apoyo y no reportó personal ocupado, dependiente y no dependiente de la razón social, en dichas funciones durante el año 2025. Corrige las variables involucradas.</t>
+  </si>
+  <si>
+    <t>20I09_2 Reconsulta con la persona informante ambas variables, ya que reportó personal capacitado en funciones operativo y de apoyo que son mujeres y no reporta personal ocupado en funciones operativo y de apoyo, dependiente y no dependiente de la razón social, que son mujeres durante el año 2025. Corrige las variables involucradas.</t>
+  </si>
+  <si>
+    <t>20I10_2 Reconsulta con la persona informante el motivo por el cual, en el gasto destinado por la empresa a la certificación de competencias laborales Conocer (Consejo Nacional de Normalización y Certificación de Competencias Laborales) durante el año 2025, se reportó un monto menor o igual a 10 pesos. 
+Deberás verificar que el resto de las variables monetarias se encuentren reportadas en pesos y no en miles de pesos. 
+Acepta justificación.</t>
+  </si>
+  <si>
+    <t>21O01_2 Revisa la descripción de «Otra» causa principal por lo que la empresa no otorgó capacitación durante el año 2025, con el fin de identificar si se puede reclasificar en los incisos anteriores.
+Acepta justificación, «Sin posibilidad de ser reclasificado».</t>
+  </si>
+  <si>
+    <t>P14_1A=0
+P14_1A&gt;0
+P17_1=0
+P17_1&gt;0</t>
+  </si>
+  <si>
+    <t>P14_2A=0
+P14_2A&gt;0
+P17_2=0
+P17_2&gt;0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPITULO </t>
+  </si>
+  <si>
+    <t>P2_9X&lt;&gt;NULL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+P5_9X&lt;&gt;NULL
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P20_2=0 OR P20_2&gt;10
+</t>
+  </si>
+  <si>
+    <t>P20_1_0A&lt;=P13_0</t>
+  </si>
+  <si>
+    <t>P20_1_1A=&lt;P14_1A</t>
+  </si>
+  <si>
+    <t>P20_1_2A=&lt;P14_2A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -458,6 +685,25 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -473,7 +719,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -484,19 +730,6 @@
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
@@ -600,75 +833,224 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1003,628 +1385,907 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C2549C4-060C-4E36-8768-B2D6C51EB8F1}">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.109375" customWidth="1"/>
     <col min="2" max="2" width="7.77734375" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="22.88671875" customWidth="1"/>
-    <col min="5" max="5" width="58.44140625" customWidth="1"/>
+    <col min="5" max="5" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23" customWidth="1"/>
+    <col min="7" max="7" width="27.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="132" x14ac:dyDescent="0.3">
+      <c r="A2" s="16">
+        <v>2</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="G2" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="H2" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A3" s="17">
+        <v>3</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E3" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="G3" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="132" x14ac:dyDescent="0.3">
+      <c r="A4" s="16">
+        <v>4</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E4" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="G4" s="37" t="s">
+        <v>120</v>
+      </c>
+      <c r="H4" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="132" x14ac:dyDescent="0.3">
+      <c r="A5" s="17">
+        <v>5</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E5" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="G5" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="H5" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A6" s="16">
+        <v>6</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E6" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="H6" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A7" s="17">
+        <v>7</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="H7" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="16">
+        <v>8</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="H8" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A9" s="17">
+        <v>9</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="H9" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="132" x14ac:dyDescent="0.3">
+      <c r="A10" s="17">
+        <v>11</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="H10" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="184.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="16">
+        <v>12</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="37" t="s">
+        <v>127</v>
+      </c>
+      <c r="H11" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="118.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="17">
+        <v>15</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" s="32" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="G12" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="H12" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="105.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="16">
+        <v>16</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="H13" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="105.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="17">
+        <v>17</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F14" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>130</v>
+      </c>
+      <c r="H14" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="105.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="16">
+        <v>18</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="G15" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="H15" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="132" x14ac:dyDescent="0.3">
+      <c r="A16" s="17">
+        <v>19</v>
+      </c>
+      <c r="B16" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="C16" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="H16" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="198" x14ac:dyDescent="0.3">
+      <c r="A17" s="16">
+        <v>20</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="H17" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="132" x14ac:dyDescent="0.3">
+      <c r="A18" s="17">
+        <v>21</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="H18" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="224.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="42">
+        <v>22</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="F19" s="44" t="s">
+        <v>150</v>
+      </c>
+      <c r="G19" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="H19" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="211.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="46">
+        <v>23</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="F20" s="44" t="s">
+        <v>151</v>
+      </c>
+      <c r="G20" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="H20" s="47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A21" s="16">
+        <v>24</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="G21" s="37" t="s">
+        <v>137</v>
+      </c>
+      <c r="H21" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A22" s="17">
+        <v>25</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F22" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="H22" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="105.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="16">
+        <v>26</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F23" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="H23" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="17">
+        <v>27</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F24" s="32" t="s">
+        <v>155</v>
+      </c>
+      <c r="G24" s="37" t="s">
+        <v>140</v>
+      </c>
+      <c r="H24" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="16">
+        <v>28</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F25" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="G25" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="H25" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="184.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="17">
+        <v>29</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F26" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="G26" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="H26" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="184.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="16">
+        <v>30</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F27" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="G27" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="H27" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="17">
+        <v>31</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F28" s="35" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="G28" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="H28" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="171.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="16">
+        <v>32</v>
+      </c>
+      <c r="B29" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="C29" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F29" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H29" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A30" s="17">
+        <v>33</v>
+      </c>
+      <c r="B30" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="5">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
+      <c r="C30" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F30" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="H30" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="171.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="16">
+        <v>34</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F31" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="H31" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="211.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="39">
+        <v>35</v>
+      </c>
+      <c r="B32" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="7"/>
+      <c r="E32" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="F32" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="G32" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="H32" s="26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="132" x14ac:dyDescent="0.3">
+      <c r="A33" s="20">
+        <v>36</v>
+      </c>
+      <c r="B33" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="5">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="5">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" s="5" t="s">
+      <c r="C33" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F33" s="20" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="53.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="5">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="5">
-        <v>18</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
-        <v>19</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="5">
-        <v>20</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
-        <v>21</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="5">
-        <v>22</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
-        <v>23</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="5">
-        <v>24</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
-        <v>25</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="5">
-        <v>26</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
-        <v>27</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="5">
-        <v>28</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D29" s="6"/>
-      <c r="E29" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
-        <v>29</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="5">
-        <v>30</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="9" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
-        <v>31</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="5">
-        <v>32</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D33" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E33" s="21" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
-        <v>33</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="5">
-        <v>34</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
-        <v>35</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" s="15"/>
-      <c r="E36" s="11" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="5">
-        <v>36</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E37" s="20" t="s">
-        <v>105</v>
-      </c>
+      <c r="G33" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="H33" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="27"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="30"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="27"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="30"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="27"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="30"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="27"/>
+      <c r="B37" s="27"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="30"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="30"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E42" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
